--- a/results/job_matches_2026-04-05.xlsx
+++ b/results/job_matches_2026-04-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
+          <t>Software Engineer - AI Agentic Product Dev Team (US)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>Eightfold</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,77 +591,77 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, Redshift, S3, SQS, SNS, RDS, Azure, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
+          <t>https://www.indeed.com/viewjob?jk=bd50de7c7c09c2ca</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer - AI Agentic Product Dev Team (US)</t>
+          <t>Senior Full Stack Developer (React)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Eightfold</t>
+          <t>Parts Authority</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, SQS, SNS, RDS, Azure, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd50de7c7c09c2ca</t>
+          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API Dev + CI/CD)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,137 +671,137 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc3ae2a8608fdd7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
+          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer, Senior</t>
+          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
+          <t>https://www.indeed.com/viewjob?jk=ede3f75e70d4727e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (React)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Parts Authority</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
+          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API Dev + CI/CD)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc3ae2a8608fdd7</t>
+          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,190 +871,15 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ede3f75e70d4727e</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Sr. Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>South Florida Community Care Network</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Sunrise, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f38270b9409d908</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>HealthEdge Software, Inc.</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>HealthEdge Software, Inc.</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
         </is>

--- a/results/job_matches_2026-04-05.xlsx
+++ b/results/job_matches_2026-04-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,122 +538,122 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer - AI Agentic Product Dev Team (US)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Eightfold</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Redshift, S3, SQS, SNS, RDS, Azure, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=170d4c1d3d53f45f</t>
+          <t>https://www.indeed.com/viewjob?jk=bd50de7c7c09c2ca</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer - AI Agentic Product Dev Team (US)</t>
+          <t>Senior Full Stack Developer (React)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Eightfold</t>
+          <t>Parts Authority</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, SQS, SNS, RDS, Azure, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd50de7c7c09c2ca</t>
+          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (React)</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API Dev + CI/CD)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Parts Authority</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc3ae2a8608fdd7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API Dev + CI/CD)</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc3ae2a8608fdd7</t>
+          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=ede3f75e70d4727e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede3f75e70d4727e</t>
+          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
         </is>
       </c>
     </row>
@@ -776,112 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>HealthEdge Software, Inc.</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-05.xlsx
+++ b/results/job_matches_2026-04-05.xlsx
@@ -538,122 +538,122 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer - AI Agentic Product Dev Team (US)</t>
+          <t>MQ - CICS Middleware Admin</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Eightfold</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, SQS, SNS, RDS, Azure, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd50de7c7c09c2ca</t>
+          <t>https://www.indeed.com/viewjob?jk=8e419b162bae199c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (React)</t>
+          <t>Software Engineer - AI Agentic Product Dev Team (US)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Parts Authority</t>
+          <t>Eightfold</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, S3, SQS, SNS, RDS, Azure, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
+          <t>https://www.indeed.com/viewjob?jk=bd50de7c7c09c2ca</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API Dev + CI/CD)</t>
+          <t>Senior Full Stack Developer (React)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Parts Authority</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc3ae2a8608fdd7</t>
+          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API Dev + CI/CD)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc3ae2a8608fdd7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede3f75e70d4727e</t>
+          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
+          <t>https://www.indeed.com/viewjob?jk=ede3f75e70d4727e</t>
         </is>
       </c>
     </row>
@@ -753,12 +753,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>St. David's HealthCare</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,17 +766,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=8645b0d44909612d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-05.xlsx
+++ b/results/job_matches_2026-04-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,315 +468,210 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C2 SMART Integration Engineer (Data Acquisition)</t>
+          <t>Software Engineer - AI Agentic Product Dev Team (US)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>I4DM</t>
+          <t>Eightfold</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>13.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks</t>
+          <t>AWS, Redshift, S3, SQS, SNS, RDS, Azure, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a2376d63bc21df</t>
+          <t>https://www.indeed.com/viewjob?jk=bd50de7c7c09c2ca</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C2 SMART Integration Engineer (Data Tagging and Availability)</t>
+          <t>Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>I4DM</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>11.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Data Factory</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d01c8b8d0caf9fe</t>
+          <t>https://www.indeed.com/viewjob?jk=863b993691d43dcd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MQ - CICS Middleware Admin</t>
+          <t>Software Engineer III – Big Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e419b162bae199c</t>
+          <t>https://www.indeed.com/viewjob?jk=c0657089c3ac9f1d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer - AI Agentic Product Dev Team (US)</t>
+          <t>Python Engineer, Senior Associate</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Eightfold</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, SQS, SNS, RDS, Azure, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd50de7c7c09c2ca</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1ed8d52cd0705a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (React)</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API Dev + CI/CD)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Parts Authority</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc3ae2a8608fdd7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API Dev + CI/CD)</t>
+          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc3ae2a8608fdd7</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Microsoft Fabric Data Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Newtown Square, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=ede3f75e70d4727e</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>St. David's HealthCare</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8645b0d44909612d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-05.xlsx
+++ b/results/job_matches_2026-04-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,33 +643,68 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Senior Backend Engineer – Node.js &amp; Microservices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>axiusSoftware</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8416ad2ad931971c</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D8" t="n">
         <v>10.4</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>2026-04-04</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ede3f75e70d4727e</t>
         </is>

--- a/results/job_matches_2026-04-05.xlsx
+++ b/results/job_matches_2026-04-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer - AI Agentic Product Dev Team (US)</t>
+          <t>Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Eightfold</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, SQS, SNS, RDS, Azure, GCP, Spark, Scala</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd50de7c7c09c2ca</t>
+          <t>https://www.indeed.com/viewjob?jk=863b993691d43dcd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Platform</t>
+          <t>Software Engineer III – Big Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=863b993691d43dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=c0657089c3ac9f1d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III – Big Data &amp; Analytics</t>
+          <t>Python Engineer, Senior Associate</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0657089c3ac9f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1ed8d52cd0705a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Python Engineer, Senior Associate</t>
+          <t>Senior Backend Engineer – Node.js &amp; Microservices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>axiusSoftware</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,110 +601,40 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1ed8d52cd0705a</t>
+          <t>https://www.indeed.com/viewjob?jk=8416ad2ad931971c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API Dev + CI/CD)</t>
+          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc3ae2a8608fdd7</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer – Node.js &amp; Microservices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>axiusSoftware</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-04-05</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8416ad2ad931971c</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Newtown Square, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ede3f75e70d4727e</t>
         </is>

--- a/results/job_matches_2026-04-05.xlsx
+++ b/results/job_matches_2026-04-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Platform</t>
+          <t>Senior Software Engineer - Python and Data Ecosystem</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Spark, Kafka, Kafka Connect, Data Modeling, dbt, Tableau, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=863b993691d43dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1ce06c12c2400c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III – Big Data &amp; Analytics</t>
+          <t>Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0657089c3ac9f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=863b993691d43dcd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Python Engineer, Senior Associate</t>
+          <t>Software Engineer III – Big Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1ed8d52cd0705a</t>
+          <t>https://www.indeed.com/viewjob?jk=c0657089c3ac9f1d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer – Node.js &amp; Microservices</t>
+          <t>Python Engineer, Senior Associate</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>axiusSoftware</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,40 +601,75 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8416ad2ad931971c</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1ed8d52cd0705a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Senior Backend Engineer – Node.js &amp; Microservices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>axiusSoftware</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8416ad2ad931971c</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" t="n">
         <v>10.4</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>2026-04-04</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ede3f75e70d4727e</t>
         </is>

--- a/results/job_matches_2026-04-05.xlsx
+++ b/results/job_matches_2026-04-05.xlsx
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python and Data Ecosystem</t>
+          <t>MQ - CICS Middleware Admin</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11.1</v>
+        <v>15.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Kafka, Kafka Connect, Data Modeling, dbt, Tableau, MLOps, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1ce06c12c2400c</t>
+          <t>https://www.indeed.com/viewjob?jk=8e419b162bae199c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Platform</t>
+          <t>Python Engineer, Senior Associate</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=863b993691d43dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1ed8d52cd0705a</t>
         </is>
       </c>
     </row>
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Python Engineer, Senior Associate</t>
+          <t>Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1ed8d52cd0705a</t>
+          <t>https://www.indeed.com/viewjob?jk=863b993691d43dcd</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-05.xlsx
+++ b/results/job_matches_2026-04-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,42 +468,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MQ - CICS Middleware Admin</t>
+          <t>Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.3</v>
+        <v>11.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e419b162bae199c</t>
+          <t>https://www.indeed.com/viewjob?jk=863b993691d43dcd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Python Engineer, Senior Associate</t>
+          <t>Software Engineer III – Big Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1ed8d52cd0705a</t>
+          <t>https://www.indeed.com/viewjob?jk=c0657089c3ac9f1d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III – Big Data &amp; Analytics</t>
+          <t>Python Engineer, Senior Associate</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0657089c3ac9f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1ed8d52cd0705a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Platform</t>
+          <t>Senior Backend Engineer – Node.js &amp; Microservices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>axiusSoftware</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,75 +601,40 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=863b993691d43dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=8416ad2ad931971c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer – Node.js &amp; Microservices</t>
+          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>axiusSoftware</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8416ad2ad931971c</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Newtown Square, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ede3f75e70d4727e</t>
         </is>

--- a/results/job_matches_2026-04-05.xlsx
+++ b/results/job_matches_2026-04-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -637,6 +637,76 @@
       <c r="G6" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ede3f75e70d4727e</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Product Architect Google Cloud Platform</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Reston Hospital Center - Reston</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9800f97130992c45</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Product Architect Google Cloud Platform</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Catholic Medical Center</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Manchester, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1dfe8d6c036c24b4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-05.xlsx
+++ b/results/job_matches_2026-04-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -637,76 +637,6 @@
       <c r="G6" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ede3f75e70d4727e</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Product Architect Google Cloud Platform</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Reston Hospital Center - Reston</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-04-05</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9800f97130992c45</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Product Architect Google Cloud Platform</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Catholic Medical Center</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Manchester, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-04-05</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1dfe8d6c036c24b4</t>
         </is>
       </c>
     </row>
